--- a/samples/multi_date_workload.xlsx
+++ b/samples/multi_date_workload.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="4月20日" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="4月21日" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="4月22日" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4月21日" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="4月22日" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="4月23日" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,161 +483,161 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>吴婷</t>
+          <t>刘洋</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>周杰</t>
+          <t>吴婷</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>孙悦</t>
+          <t>周杰</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>6</v>
       </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>8</v>
-      </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>孙悦</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -647,37 +647,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -687,37 +687,37 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="n">
         <v>12</v>
       </c>
-      <c r="C7" t="n">
-        <v>10</v>
-      </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -727,34 +727,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -767,37 +767,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -807,34 +807,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>5</v>
@@ -868,10 +868,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -887,37 +887,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1003,37 +1003,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1043,37 +1043,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1083,37 +1083,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1123,34 +1123,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -1163,37 +1163,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1203,37 +1203,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1246,31 +1246,31 @@
         <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -1283,37 +1283,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1323,34 +1323,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -1363,34 +1363,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -1403,37 +1403,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1446,34 +1446,34 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1559,37 +1559,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
         <v>8</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
       <c r="J2" t="n">
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1599,37 +1599,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1639,194 +1639,194 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>孙悦</t>
+          <t>张伟</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>李娜</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
         <v>7</v>
       </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>8</v>
-      </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>李娜</t>
+          <t>杨帆</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>杨帆</t>
+          <t>赵敏</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -1835,38 +1835,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>赵敏</t>
+          <t>郑凯</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>3</v>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
         <v>20</v>
@@ -1888,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
@@ -1900,16 +1900,16 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1919,28 +1919,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/samples/multi_date_workload.xlsx
+++ b/samples/multi_date_workload.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C2" t="n">
         <v>6</v>
       </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -527,34 +527,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>3</v>
@@ -567,34 +567,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -607,173 +607,173 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
         <v>6</v>
       </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>李娜</t>
+          <t>张伟</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>杨帆</t>
+          <t>李娜</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>王强</t>
+          <t>杨帆</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>赵敏</t>
+          <t>王强</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -782,59 +782,59 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>郑凯</t>
+          <t>赵敏</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>3</v>
@@ -847,37 +847,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -887,28 +887,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
         <v>5</v>
@@ -917,7 +917,7 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -931,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1003,37 +1003,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4</v>
-      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1043,34 +1043,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -1083,37 +1083,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1123,25 +1123,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1163,37 +1163,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1203,16 +1203,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -1224,13 +1224,13 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1243,28 +1243,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1283,34 +1283,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -1323,74 +1323,74 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>郑凯</t>
+          <t>陈晨</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -1399,81 +1399,41 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>陈晨</t>
+          <t>黄丽</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>黄丽</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" t="n">
-        <v>18</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1559,31 +1519,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -1599,31 +1559,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -1639,117 +1599,117 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
         <v>8</v>
       </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>孙悦</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
         <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>李娜</t>
+          <t>张伟</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
         <v>6</v>
       </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>7</v>
-      </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1759,77 +1719,77 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>赵敏</t>
+          <t>王强</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1839,37 +1799,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1879,19 +1839,19 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
         <v>8</v>
       </c>
-      <c r="C10" t="n">
-        <v>20</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
@@ -1900,16 +1860,16 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1922,34 +1882,34 @@
         <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
